--- a/Card stats.xlsx
+++ b/Card stats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vladimir Verchinine\Caliber Dropbox\Group Caliber\Data Science Team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vladimir Verchinine\Caliber Dropbox\Vladimir Verchinine\PC\Desktop\football-caliber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3530CE36-B3AA-4EC9-A0E2-7FB336BCE9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92897718-56E6-42C5-8A87-5EC760B337F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1549,13 +1549,21 @@
       <c r="B42" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="C42" s="4">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
+      <c r="F42" s="4">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
@@ -1564,13 +1572,21 @@
       <c r="B43" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
+      <c r="C43" s="6">
+        <v>0</v>
+      </c>
+      <c r="D43" s="6">
+        <v>0</v>
+      </c>
       <c r="E43" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
+      <c r="F43" s="6">
+        <v>0</v>
+      </c>
+      <c r="G43" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
@@ -1579,13 +1595,21 @@
       <c r="B44" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
+      <c r="C44" s="4">
+        <v>2</v>
+      </c>
+      <c r="D44" s="4">
+        <v>0</v>
+      </c>
       <c r="E44" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
+      <c r="F44" s="4">
+        <v>2</v>
+      </c>
+      <c r="G44" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1594,13 +1618,21 @@
       <c r="B45" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
+      <c r="C45" s="6">
+        <v>1</v>
+      </c>
+      <c r="D45" s="6">
+        <v>0</v>
+      </c>
       <c r="E45" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
+      <c r="F45" s="6">
+        <v>1</v>
+      </c>
+      <c r="G45" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="4">

--- a/Card stats.xlsx
+++ b/Card stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vladimir Verchinine\Caliber Dropbox\Vladimir Verchinine\PC\Desktop\football-caliber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92897718-56E6-42C5-8A87-5EC760B337F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB73B144-EE87-46E6-8CA3-026B88B0172F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1641,13 +1641,21 @@
       <c r="B46" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
+      <c r="C46" s="4">
+        <v>1</v>
+      </c>
+      <c r="D46" s="4">
+        <v>0</v>
+      </c>
       <c r="E46" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
+      <c r="F46" s="4">
+        <v>1</v>
+      </c>
+      <c r="G46" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
@@ -1656,13 +1664,21 @@
       <c r="B47" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
+      <c r="C47" s="6">
+        <v>1</v>
+      </c>
+      <c r="D47" s="6">
+        <v>0</v>
+      </c>
       <c r="E47" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
+      <c r="F47" s="6">
+        <v>1</v>
+      </c>
+      <c r="G47" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
@@ -1671,13 +1687,21 @@
       <c r="B48" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
+      <c r="C48" s="4">
+        <v>1</v>
+      </c>
+      <c r="D48" s="4">
+        <v>0</v>
+      </c>
       <c r="E48" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
+      <c r="F48" s="4">
+        <v>1</v>
+      </c>
+      <c r="G48" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
@@ -1686,13 +1710,21 @@
       <c r="B49" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
+      <c r="C49" s="6">
+        <v>2</v>
+      </c>
+      <c r="D49" s="6">
+        <v>0</v>
+      </c>
       <c r="E49" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
+      <c r="F49" s="6">
+        <v>1</v>
+      </c>
+      <c r="G49" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="4">

--- a/Card stats.xlsx
+++ b/Card stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vladimir Verchinine\Caliber Dropbox\Vladimir Verchinine\PC\Desktop\football-caliber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB73B144-EE87-46E6-8CA3-026B88B0172F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32268ACB-E2D6-4CF5-B04B-0622C6E8465C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1733,13 +1733,21 @@
       <c r="B50" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
+      <c r="C50" s="4">
+        <v>1</v>
+      </c>
+      <c r="D50" s="4">
+        <v>0</v>
+      </c>
       <c r="E50" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
+      <c r="F50" s="4">
+        <v>1</v>
+      </c>
+      <c r="G50" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
@@ -1748,13 +1756,21 @@
       <c r="B51" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
+      <c r="C51" s="6">
+        <v>1</v>
+      </c>
+      <c r="D51" s="6">
+        <v>0</v>
+      </c>
       <c r="E51" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
+      <c r="F51" s="6">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
@@ -1763,13 +1779,21 @@
       <c r="B52" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
+      <c r="C52" s="4">
+        <v>1</v>
+      </c>
+      <c r="D52" s="4">
+        <v>0</v>
+      </c>
       <c r="E52" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
+      <c r="F52" s="4">
+        <v>2</v>
+      </c>
+      <c r="G52" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
@@ -1778,13 +1802,21 @@
       <c r="B53" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
+      <c r="C53" s="6">
+        <v>1</v>
+      </c>
+      <c r="D53" s="6">
+        <v>0</v>
+      </c>
       <c r="E53" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
+      <c r="F53" s="6">
+        <v>1</v>
+      </c>
+      <c r="G53" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
@@ -1793,13 +1825,21 @@
       <c r="B54" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
+      <c r="C54" s="4">
+        <v>1</v>
+      </c>
+      <c r="D54" s="4">
+        <v>0</v>
+      </c>
       <c r="E54" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
+      <c r="F54" s="4">
+        <v>2</v>
+      </c>
+      <c r="G54" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
@@ -1808,13 +1848,21 @@
       <c r="B55" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
+      <c r="C55" s="6">
+        <v>0</v>
+      </c>
+      <c r="D55" s="6">
+        <v>0</v>
+      </c>
       <c r="E55" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
+      <c r="F55" s="6">
+        <v>3</v>
+      </c>
+      <c r="G55" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="4">

--- a/Card stats.xlsx
+++ b/Card stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vladimir Verchinine\Caliber Dropbox\Vladimir Verchinine\PC\Desktop\football-caliber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32268ACB-E2D6-4CF5-B04B-0622C6E8465C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438FBF16-794F-4966-9F7B-1484C22A25B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1397,13 +1397,21 @@
       <c r="B34" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
+      <c r="C34" s="4">
+        <v>2</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
+      <c r="F34" s="4">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
@@ -1412,13 +1420,21 @@
       <c r="B35" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
+      <c r="C35" s="6">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6">
+        <v>0</v>
+      </c>
       <c r="E35" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
+      <c r="F35" s="6">
+        <v>1</v>
+      </c>
+      <c r="G35" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
@@ -1427,13 +1443,21 @@
       <c r="B36" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
+      <c r="C36" s="4">
+        <v>1</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
+      <c r="F36" s="4">
+        <v>2</v>
+      </c>
+      <c r="G36" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
@@ -1442,13 +1466,21 @@
       <c r="B37" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
+      <c r="C37" s="6">
+        <v>0</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0</v>
+      </c>
       <c r="E37" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
+      <c r="F37" s="6">
+        <v>0</v>
+      </c>
+      <c r="G37" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
@@ -1871,13 +1903,21 @@
       <c r="B56" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
+      <c r="C56" s="4">
+        <v>0</v>
+      </c>
+      <c r="D56" s="4">
+        <v>0</v>
+      </c>
       <c r="E56" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
+      <c r="F56" s="4">
+        <v>1</v>
+      </c>
+      <c r="G56" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
@@ -1886,13 +1926,21 @@
       <c r="B57" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
+      <c r="C57" s="6">
+        <v>0</v>
+      </c>
+      <c r="D57" s="6">
+        <v>0</v>
+      </c>
       <c r="E57" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
+      <c r="F57" s="6">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="4">

--- a/Card stats.xlsx
+++ b/Card stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vladimir Verchinine\Caliber Dropbox\Vladimir Verchinine\PC\Desktop\football-caliber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438FBF16-794F-4966-9F7B-1484C22A25B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FD6199-8676-4A4D-AEB5-538CD8E78430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2041,13 +2041,21 @@
       <c r="B62" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
+      <c r="C62" s="4">
+        <v>3</v>
+      </c>
+      <c r="D62" s="4">
+        <v>0</v>
+      </c>
       <c r="E62" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
+      <c r="F62" s="4">
+        <v>4</v>
+      </c>
+      <c r="G62" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
@@ -2056,13 +2064,21 @@
       <c r="B63" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
+      <c r="C63" s="6">
+        <v>2</v>
+      </c>
+      <c r="D63" s="6">
+        <v>0</v>
+      </c>
       <c r="E63" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
+      <c r="F63" s="6">
+        <v>0</v>
+      </c>
+      <c r="G63" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
@@ -2071,13 +2087,21 @@
       <c r="B64" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
+      <c r="C64" s="4">
+        <v>1</v>
+      </c>
+      <c r="D64" s="4">
+        <v>0</v>
+      </c>
       <c r="E64" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
+      <c r="F64" s="4">
+        <v>3</v>
+      </c>
+      <c r="G64" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
@@ -2086,13 +2110,21 @@
       <c r="B65" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
+      <c r="C65" s="6">
+        <v>3</v>
+      </c>
+      <c r="D65" s="6">
+        <v>1</v>
+      </c>
       <c r="E65" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
+      <c r="F65" s="6">
+        <v>1</v>
+      </c>
+      <c r="G65" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
@@ -2101,13 +2133,21 @@
       <c r="B66" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
+      <c r="C66" s="4">
+        <v>1</v>
+      </c>
+      <c r="D66" s="4">
+        <v>0</v>
+      </c>
       <c r="E66" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
+      <c r="F66" s="4">
+        <v>1</v>
+      </c>
+      <c r="G66" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2116,13 +2156,21 @@
       <c r="B67" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
+      <c r="C67" s="6">
+        <v>2</v>
+      </c>
+      <c r="D67" s="6">
+        <v>0</v>
+      </c>
       <c r="E67" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
+      <c r="F67" s="6">
+        <v>2</v>
+      </c>
+      <c r="G67" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="4">

--- a/Card stats.xlsx
+++ b/Card stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vladimir Verchinine\Caliber Dropbox\Vladimir Verchinine\PC\Desktop\football-caliber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FD6199-8676-4A4D-AEB5-538CD8E78430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B970F38-DB5C-46F2-A90C-A621D423A503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2179,13 +2179,21 @@
       <c r="B68" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
+      <c r="C68" s="4">
+        <v>0</v>
+      </c>
+      <c r="D68" s="4">
+        <v>0</v>
+      </c>
       <c r="E68" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
+      <c r="F68" s="4">
+        <v>1</v>
+      </c>
+      <c r="G68" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
@@ -2194,13 +2202,21 @@
       <c r="B69" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
+      <c r="C69" s="6">
+        <v>3</v>
+      </c>
+      <c r="D69" s="6">
+        <v>0</v>
+      </c>
       <c r="E69" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
+      <c r="F69" s="6">
+        <v>0</v>
+      </c>
+      <c r="G69" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
@@ -2209,13 +2225,21 @@
       <c r="B70" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
+      <c r="C70" s="4">
+        <v>3</v>
+      </c>
+      <c r="D70" s="4">
+        <v>0</v>
+      </c>
       <c r="E70" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
+      <c r="F70" s="4">
+        <v>2</v>
+      </c>
+      <c r="G70" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
@@ -2224,13 +2248,21 @@
       <c r="B71" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
+      <c r="C71" s="6">
+        <v>1</v>
+      </c>
+      <c r="D71" s="6">
+        <v>0</v>
+      </c>
       <c r="E71" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
+      <c r="F71" s="6">
+        <v>0</v>
+      </c>
+      <c r="G71" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
@@ -2239,13 +2271,21 @@
       <c r="B72" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
+      <c r="C72" s="4">
+        <v>2</v>
+      </c>
+      <c r="D72" s="4">
+        <v>0</v>
+      </c>
       <c r="E72" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
+      <c r="F72" s="4">
+        <v>1</v>
+      </c>
+      <c r="G72" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
@@ -2254,13 +2294,21 @@
       <c r="B73" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
+      <c r="C73" s="6">
+        <v>1</v>
+      </c>
+      <c r="D73" s="6">
+        <v>0</v>
+      </c>
       <c r="E73" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
+      <c r="F73" s="6">
+        <v>1</v>
+      </c>
+      <c r="G73" s="6">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G73" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
